--- a/forms/trg/Formulir_TRG_crem.xlsx
+++ b/forms/trg/Formulir_TRG_crem.xlsx
@@ -916,7 +916,11 @@
           <t>Dr. Eng. Lukmanul Hakim Arma</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Associate Professor, Department of Mechanical Engineering, Faculty of Engineering, Hasanuddin University, Indonesia</t>
